--- a/test_data/Orion_Stress_Demo/PN-ALPHA-01/30101/BU 03/HRM/post FET_HRM-2031-0152/Panel-28/coupon_back/2031-03-01_08-00-00_ENG_Orion_Stress_Demo_BU03_Coupon_Back_Summary.xlsx
+++ b/test_data/Orion_Stress_Demo/PN-ALPHA-01/30101/BU 03/HRM/post FET_HRM-2031-0152/Panel-28/coupon_back/2031-03-01_08-00-00_ENG_Orion_Stress_Demo_BU03_Coupon_Back_Summary.xlsx
@@ -460,22 +460,22 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>16.88581</v>
+        <v>16.91499</v>
       </c>
       <c r="D2" t="n">
-        <v>16.6732</v>
+        <v>16.69231</v>
       </c>
       <c r="E2" t="n">
-        <v>16.62219</v>
+        <v>16.71212</v>
       </c>
       <c r="F2" t="n">
-        <v>43.32812</v>
+        <v>43.25929</v>
       </c>
       <c r="G2" t="n">
-        <v>0.05108</v>
+        <v>0.05046</v>
       </c>
       <c r="H2" t="n">
-        <v>1.85034</v>
+        <v>1.84782</v>
       </c>
     </row>
     <row r="3">
@@ -485,22 +485,22 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>16.83299</v>
+        <v>17.01441</v>
       </c>
       <c r="D3" t="n">
-        <v>16.69629</v>
+        <v>16.70828</v>
       </c>
       <c r="E3" t="n">
-        <v>16.93266</v>
+        <v>16.73958</v>
       </c>
       <c r="F3" t="n">
-        <v>42.48251</v>
+        <v>43.89527</v>
       </c>
       <c r="G3" t="n">
-        <v>0.05043</v>
+        <v>0.05123</v>
       </c>
       <c r="H3" t="n">
-        <v>1.8108</v>
+        <v>1.84728</v>
       </c>
     </row>
     <row r="4">
@@ -510,22 +510,22 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>16.71604</v>
+        <v>17.11861</v>
       </c>
       <c r="D4" t="n">
-        <v>16.58396</v>
+        <v>16.78651</v>
       </c>
       <c r="E4" t="n">
-        <v>16.77062</v>
+        <v>16.81606</v>
       </c>
       <c r="F4" t="n">
-        <v>42.23378</v>
+        <v>42.02802</v>
       </c>
       <c r="G4" t="n">
-        <v>0.05131</v>
+        <v>0.05035</v>
       </c>
       <c r="H4" t="n">
-        <v>1.82479</v>
+        <v>1.80417</v>
       </c>
     </row>
     <row r="5">
@@ -567,19 +567,19 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>16.93225</v>
+        <v>16.80084</v>
       </c>
       <c r="D6" t="n">
-        <v>16.38271</v>
+        <v>15.90154</v>
       </c>
       <c r="E6" t="n">
-        <v>16.68801</v>
+        <v>16.54952</v>
       </c>
       <c r="F6" t="n">
-        <v>22.08156</v>
+        <v>21.68836</v>
       </c>
       <c r="G6" t="n">
-        <v>33.09804</v>
+        <v>34.15468</v>
       </c>
     </row>
     <row r="7">
@@ -589,19 +589,19 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>16.83989</v>
+        <v>16.78792</v>
       </c>
       <c r="D7" t="n">
-        <v>15.96544</v>
+        <v>16.17291</v>
       </c>
       <c r="E7" t="n">
-        <v>16.20604</v>
+        <v>16.54692</v>
       </c>
       <c r="F7" t="n">
-        <v>22.40728</v>
+        <v>21.91152</v>
       </c>
       <c r="G7" t="n">
-        <v>33.50265</v>
+        <v>34.27426</v>
       </c>
     </row>
     <row r="8">
@@ -611,19 +611,19 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>16.94825</v>
+        <v>16.66066</v>
       </c>
       <c r="D8" t="n">
-        <v>15.64592</v>
+        <v>16.16072</v>
       </c>
       <c r="E8" t="n">
-        <v>16.59535</v>
+        <v>16.33727</v>
       </c>
       <c r="F8" t="n">
-        <v>21.87535</v>
+        <v>22.11482</v>
       </c>
       <c r="G8" t="n">
-        <v>34.07941</v>
+        <v>34.43987</v>
       </c>
     </row>
     <row r="9">
@@ -650,10 +650,10 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>0.61303</v>
+        <v>0.59892</v>
       </c>
       <c r="D10" t="n">
-        <v>1.12226</v>
+        <v>1.14014</v>
       </c>
     </row>
     <row r="11">
@@ -663,10 +663,10 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>0.61408</v>
+        <v>0.62002</v>
       </c>
       <c r="D11" t="n">
-        <v>1.10601</v>
+        <v>1.10752</v>
       </c>
     </row>
     <row r="12">
@@ -676,10 +676,10 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>0.60529</v>
+        <v>0.6087399999999999</v>
       </c>
       <c r="D12" t="n">
-        <v>1.12494</v>
+        <v>1.1172</v>
       </c>
     </row>
   </sheetData>
